--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9962c7f76b6a4648"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R30f70c69fc5c4c7b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -22,14 +22,6 @@
       <x:b/>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:sz val="9"/>
-      <x:name val="宋体"/>
     </x:font>
   </x:fonts>
   <x:fills count="4">
@@ -50,33 +42,14 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="2">
-    <x:border/>
+  <x:borders count="1">
     <x:border/>
   </x:borders>
-  <x:cellStyleXfs count="2">
+  <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
   <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -84,17 +57,38 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -103,9 +97,8 @@
       </x:extLst>
     </x:xf>
   </x:cellXfs>
-  <x:cellStyles count="2">
-    <x:cellStyle name="Normal" xfId="1"/>
-    <x:cellStyle name="常规" xfId="0"/>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
 </file>
@@ -274,562 +267,695 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="14.25"/>
-  <x:cols>
-    <x:col min="1" max="1" width="9.25" customWidth="1"/>
-    <x:col min="2" max="2" width="32.125" customWidth="1"/>
-    <x:col min="3" max="3" width="26.375" customWidth="1"/>
-    <x:col min="4" max="4" width="20.75" customWidth="1"/>
-    <x:col min="5" max="5" width="50.75" customWidth="1"/>
-    <x:col min="6" max="6" width="23.625" customWidth="1"/>
-    <x:col min="7" max="8" width="12.125" customWidth="1"/>
-    <x:col min="9" max="9" width="42.125" customWidth="1"/>
-    <x:col min="10" max="10" width="13.625" customWidth="1"/>
-    <x:col min="11" max="11" width="25" customWidth="1"/>
-  </x:cols>
+  <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="30">
-      <x:c r="A1" s="2" t="str">
+    <x:row r="1">
+      <x:c r="A1" s="7" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="str">
+      <x:c r="B1" s="7" t="str">
         <x:v>full_name</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="str">
+      <x:c r="C1" s="7" t="str">
         <x:v>value_type</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="str">
+      <x:c r="D1" s="7" t="str">
         <x:v>read_schema_from_file</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="str">
+      <x:c r="E1" s="7" t="str">
         <x:v>input</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="str">
+      <x:c r="F1" s="7" t="str">
         <x:v>index</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="str">
+      <x:c r="G1" s="7" t="str">
         <x:v>mode</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="str">
+      <x:c r="H1" s="7" t="str">
         <x:v>group</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="str">
+      <x:c r="I1" s="7" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="str">
+      <x:c r="J1" s="7" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="str">
+      <x:c r="K1" s="7" t="str">
         <x:v>output</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="3" t="str">
+      <x:c r="A2" s="8" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="B2" s="8" t="str">
         <x:v>全名(包含模块和名字)</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str">
+      <x:c r="C2" s="8" t="str">
         <x:v>记录类名</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="D2" s="8" t="str">
         <x:v>从excel读取定义</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
+      <x:c r="E2" s="8" t="str">
         <x:v>文件列表</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="str">
+      <x:c r="F2" s="8" t="str">
         <x:v>表id字段</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="str">
+      <x:c r="G2" s="8" t="str">
         <x:v>模式</x:v>
       </x:c>
-      <x:c r="H2" s="3" t="str">
+      <x:c r="H2" s="8" t="str">
         <x:v>分组</x:v>
       </x:c>
-      <x:c r="I2" s="3" t="str">
+      <x:c r="I2" s="8" t="str">
         <x:v>注释</x:v>
       </x:c>
-      <x:c r="J2" s="3"/>
-      <x:c r="K2" s="3" t="str">
+      <x:c r="J2" s="8"/>
+      <x:c r="K2" s="8" t="str">
         <x:v>输出文件名</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="71.25">
-      <x:c r="A3" s="3" t="str">
+    <x:row r="3">
+      <x:c r="A3" s="8" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3" s="3"/>
-      <x:c r="C3" s="3"/>
-      <x:c r="D3" s="3" t="str">
+      <x:c r="B3" s="8"/>
+      <x:c r="C3" s="8"/>
+      <x:c r="D3" s="8" t="str">
         <x:v>false时取已有定义，true为从excel标题头和属性栏读取定义</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="str">
+      <x:c r="E3" s="8" t="str">
         <x:v>可以多个，以逗号','分隔；多Sheet工作簿使用 SheetName@file.xlsx</x:v>
       </x:c>
-      <x:c r="F3" s="3" t="str">
+      <x:c r="F3" s="8" t="str">
         <x:v>单主键 map 表填写主键字段；关系表建议用 list，由业务层自行建立复合索引</x:v>
       </x:c>
-      <x:c r="G3" s="3" t="str">
+      <x:c r="G3" s="8" t="str">
         <x:v>取值one|map|list，为空自动为map</x:v>
       </x:c>
-      <x:c r="H3" s="3" t="str">
+      <x:c r="H3" s="8" t="str">
         <x:v>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</x:v>
       </x:c>
-      <x:c r="I3" s="3"/>
-      <x:c r="J3" s="3"/>
-      <x:c r="K3" s="3" t="str">
+      <x:c r="I3" s="8"/>
+      <x:c r="J3" s="8"/>
+      <x:c r="K3" s="8" t="str">
         <x:v>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="1"/>
-      <x:c r="B4" s="1" t="str">
+      <x:c r="A4" s="5"/>
+      <x:c r="B4" s="5" t="str">
         <x:v>item.TbItem</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="str">
+      <x:c r="C4" s="5" t="str">
         <x:v>Item</x:v>
       </x:c>
-      <x:c r="D4" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="str">
+      <x:c r="D4" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="5" t="str">
         <x:v>item.xlsx</x:v>
       </x:c>
-      <x:c r="F4" s="1"/>
-      <x:c r="G4" s="1"/>
-      <x:c r="H4" s="1"/>
-      <x:c r="I4" s="1" t="str">
+      <x:c r="F4" s="5"/>
+      <x:c r="G4" s="5"/>
+      <x:c r="H4" s="5"/>
+      <x:c r="I4" s="5" t="str">
         <x:v>TEngine 示例道具表</x:v>
       </x:c>
-      <x:c r="J4" s="1"/>
-      <x:c r="K4" s="1"/>
+      <x:c r="J4" s="5"/>
+      <x:c r="K4" s="5"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="1"/>
-      <x:c r="B5" s="1" t="str">
+      <x:c r="A5" s="5"/>
+      <x:c r="B5" s="5" t="str">
         <x:v>dnd.TbRulePackage</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="str">
+      <x:c r="C5" s="5" t="str">
         <x:v>RulePackage</x:v>
       </x:c>
-      <x:c r="D5" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="str">
+      <x:c r="D5" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="5" t="str">
         <x:v>TbRulePackage@dnd_rule_content_luban_template.xlsx</x:v>
       </x:c>
-      <x:c r="F5" s="1" t="str">
+      <x:c r="F5" s="5" t="str">
         <x:v>package_id</x:v>
       </x:c>
-      <x:c r="G5" s="1" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H5" s="1" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="I5" s="1" t="str">
+      <x:c r="G5" s="5" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H5" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I5" s="5" t="str">
         <x:v>规则包定义表</x:v>
       </x:c>
-      <x:c r="J5" s="1"/>
-      <x:c r="K5" s="1"/>
+      <x:c r="J5" s="5"/>
+      <x:c r="K5" s="5"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="1"/>
-      <x:c r="B6" s="1" t="str">
+      <x:c r="A6" s="5"/>
+      <x:c r="B6" s="5" t="str">
         <x:v>dnd.TbClassDefine</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="str">
+      <x:c r="C6" s="5" t="str">
         <x:v>ClassDefine</x:v>
       </x:c>
-      <x:c r="D6" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="str">
+      <x:c r="D6" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="5" t="str">
         <x:v>TbClassDefine@dnd_rule_content_luban_template.xlsx</x:v>
       </x:c>
-      <x:c r="F6" s="1" t="str">
+      <x:c r="F6" s="5" t="str">
         <x:v>class_id</x:v>
       </x:c>
-      <x:c r="G6" s="1" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H6" s="1" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="I6" s="1" t="str">
+      <x:c r="G6" s="5" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H6" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I6" s="5" t="str">
         <x:v>职业定义表</x:v>
       </x:c>
-      <x:c r="J6" s="1"/>
-      <x:c r="K6" s="1"/>
-    </x:row>
-    <x:row r="7" ht="28.5">
-      <x:c r="A7" s="1"/>
-      <x:c r="B7" s="1" t="str">
+      <x:c r="J6" s="5"/>
+      <x:c r="K6" s="5"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="5"/>
+      <x:c r="B7" s="5" t="str">
         <x:v>dnd.TbClassLevelProgression</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="str">
+      <x:c r="C7" s="5" t="str">
         <x:v>ClassLevelProgression</x:v>
       </x:c>
-      <x:c r="D7" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="str">
+      <x:c r="D7" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" s="5" t="str">
         <x:v>TbClassLevelProgression@dnd_rule_content_luban_template.xlsx</x:v>
       </x:c>
-      <x:c r="F7" s="1"/>
-      <x:c r="G7" s="1" t="str">
+      <x:c r="F7" s="5"/>
+      <x:c r="G7" s="5" t="str">
         <x:v>list</x:v>
       </x:c>
-      <x:c r="H7" s="1" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="I7" s="1" t="str">
+      <x:c r="H7" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I7" s="5" t="str">
         <x:v>职业1-20级成长表。业务层按 class_id + level 查询。</x:v>
       </x:c>
-      <x:c r="J7" s="1"/>
-      <x:c r="K7" s="1"/>
+      <x:c r="J7" s="5"/>
+      <x:c r="K7" s="5"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="1"/>
-      <x:c r="B8" s="1" t="str">
+      <x:c r="A8" s="5"/>
+      <x:c r="B8" s="5" t="str">
         <x:v>dnd.TbFeatureDefine</x:v>
       </x:c>
-      <x:c r="C8" s="1" t="str">
+      <x:c r="C8" s="5" t="str">
         <x:v>FeatureDefine</x:v>
       </x:c>
-      <x:c r="D8" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="str">
+      <x:c r="D8" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="5" t="str">
         <x:v>TbFeatureDefine@dnd_rule_content_luban_template.xlsx</x:v>
       </x:c>
-      <x:c r="F8" s="1" t="str">
+      <x:c r="F8" s="5" t="str">
         <x:v>feature_id</x:v>
       </x:c>
-      <x:c r="G8" s="1" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H8" s="1" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="I8" s="1" t="str">
+      <x:c r="G8" s="5" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H8" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I8" s="5" t="str">
         <x:v>职业/种族/背景/专长/法术特性定义表</x:v>
       </x:c>
-      <x:c r="J8" s="1"/>
-      <x:c r="K8" s="1"/>
+      <x:c r="J8" s="5"/>
+      <x:c r="K8" s="5"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="1"/>
-      <x:c r="B9" s="1" t="str">
+      <x:c r="A9" s="5"/>
+      <x:c r="B9" s="5" t="str">
         <x:v>dnd.TbFeatureEffect</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="str">
+      <x:c r="C9" s="5" t="str">
         <x:v>FeatureEffect</x:v>
       </x:c>
-      <x:c r="D9" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="str">
+      <x:c r="D9" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="5" t="str">
         <x:v>TbFeatureEffect@dnd_rule_content_luban_template.xlsx</x:v>
       </x:c>
-      <x:c r="F9" s="1" t="str">
+      <x:c r="F9" s="5" t="str">
         <x:v>effect_id</x:v>
       </x:c>
-      <x:c r="G9" s="1" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H9" s="1" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="I9" s="1" t="str">
+      <x:c r="G9" s="5" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H9" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I9" s="5" t="str">
         <x:v>结构化特性效果表</x:v>
       </x:c>
-      <x:c r="J9" s="1"/>
-      <x:c r="K9" s="1"/>
+      <x:c r="J9" s="5"/>
+      <x:c r="K9" s="5"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="1"/>
-      <x:c r="B10" s="1" t="str">
+      <x:c r="A10" s="5"/>
+      <x:c r="B10" s="5" t="str">
         <x:v>dnd.TbChoiceGroup</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="str">
+      <x:c r="C10" s="5" t="str">
         <x:v>ChoiceGroup</x:v>
       </x:c>
-      <x:c r="D10" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="str">
+      <x:c r="D10" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" s="5" t="str">
         <x:v>TbChoiceGroup@dnd_rule_content_luban_template.xlsx</x:v>
       </x:c>
-      <x:c r="F10" s="1" t="str">
+      <x:c r="F10" s="5" t="str">
         <x:v>choice_group_id</x:v>
       </x:c>
-      <x:c r="G10" s="1" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H10" s="1" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="I10" s="1" t="str">
+      <x:c r="G10" s="5" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H10" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I10" s="5" t="str">
         <x:v>角色创建与升级选择组表</x:v>
       </x:c>
-      <x:c r="J10" s="1"/>
-      <x:c r="K10" s="1"/>
-    </x:row>
-    <x:row r="11" ht="28.5">
-      <x:c r="A11" s="1"/>
-      <x:c r="B11" s="1" t="str">
+      <x:c r="J10" s="5"/>
+      <x:c r="K10" s="5"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="5"/>
+      <x:c r="B11" s="5" t="str">
         <x:v>dnd.TbChoiceOption</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="str">
+      <x:c r="C11" s="5" t="str">
         <x:v>ChoiceOption</x:v>
       </x:c>
-      <x:c r="D11" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="str">
+      <x:c r="D11" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" s="5" t="str">
         <x:v>TbChoiceOption@dnd_rule_content_luban_template.xlsx</x:v>
       </x:c>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="1" t="str">
+      <x:c r="F11" s="5"/>
+      <x:c r="G11" s="5" t="str">
         <x:v>list</x:v>
       </x:c>
-      <x:c r="H11" s="1" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="I11" s="1" t="str">
+      <x:c r="H11" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I11" s="5" t="str">
         <x:v>选择组选项表。业务层按 choice_group_id + option_id 查询。</x:v>
       </x:c>
-      <x:c r="J11" s="1"/>
-      <x:c r="K11" s="1"/>
+      <x:c r="J11" s="5"/>
+      <x:c r="K11" s="5"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="1"/>
-      <x:c r="B12" s="1" t="str">
+      <x:c r="A12" s="5"/>
+      <x:c r="B12" s="5" t="str">
         <x:v>dnd.TbRaceMainDefine</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="str">
+      <x:c r="C12" s="5" t="str">
         <x:v>RaceMainDefine</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="str">
+      <x:c r="D12" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="5" t="str">
         <x:v>TbRaceMainDefine@dnd_rule_content_luban_template.xlsx</x:v>
       </x:c>
-      <x:c r="F12" s="1" t="str">
+      <x:c r="F12" s="5" t="str">
         <x:v>main_race_id</x:v>
       </x:c>
-      <x:c r="G12" s="1" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H12" s="1" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="I12" s="1" t="str">
+      <x:c r="G12" s="5" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H12" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I12" s="5" t="str">
         <x:v>主要种族定义表</x:v>
       </x:c>
-      <x:c r="J12" s="1"/>
-      <x:c r="K12" s="1"/>
+      <x:c r="J12" s="5"/>
+      <x:c r="K12" s="5"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="1"/>
-      <x:c r="B13" s="1" t="str">
+      <x:c r="A13" s="5"/>
+      <x:c r="B13" s="5" t="str">
         <x:v>dnd.TbRaceSubDefine</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="str">
+      <x:c r="C13" s="5" t="str">
         <x:v>RaceSubDefine</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="str">
+      <x:c r="D13" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" s="5" t="str">
         <x:v>TbRaceSubDefine@dnd_rule_content_luban_template.xlsx</x:v>
       </x:c>
-      <x:c r="F13" s="1" t="str">
+      <x:c r="F13" s="5" t="str">
         <x:v>sub_race_id</x:v>
       </x:c>
-      <x:c r="G13" s="1" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H13" s="1" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="I13" s="1" t="str">
+      <x:c r="G13" s="5" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H13" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I13" s="5" t="str">
         <x:v>亚种定义表</x:v>
       </x:c>
-      <x:c r="J13" s="1"/>
-      <x:c r="K13" s="1"/>
+      <x:c r="J13" s="5"/>
+      <x:c r="K13" s="5"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="1"/>
-      <x:c r="B14" s="1" t="str">
+      <x:c r="A14" s="5"/>
+      <x:c r="B14" s="5" t="str">
         <x:v>dnd.TbBackgroundDefine</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="str">
+      <x:c r="C14" s="5" t="str">
         <x:v>BackgroundDefine</x:v>
       </x:c>
-      <x:c r="D14" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="str">
+      <x:c r="D14" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" s="5" t="str">
         <x:v>TbBackgroundDefine@dnd_rule_content_luban_template.xlsx</x:v>
       </x:c>
-      <x:c r="F14" s="1" t="str">
+      <x:c r="F14" s="5" t="str">
         <x:v>background_id</x:v>
       </x:c>
-      <x:c r="G14" s="1" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H14" s="1" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="I14" s="1" t="str">
+      <x:c r="G14" s="5" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H14" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I14" s="5" t="str">
         <x:v>背景定义表</x:v>
       </x:c>
-      <x:c r="J14" s="1"/>
-      <x:c r="K14" s="1"/>
+      <x:c r="J14" s="5"/>
+      <x:c r="K14" s="5"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="1"/>
-      <x:c r="B15" s="1" t="str">
+      <x:c r="A15" s="5"/>
+      <x:c r="B15" s="5" t="str">
         <x:v>dnd.TbFeatDefine</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="str">
+      <x:c r="C15" s="5" t="str">
         <x:v>FeatDefine</x:v>
       </x:c>
-      <x:c r="D15" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="str">
+      <x:c r="D15" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" s="5" t="str">
         <x:v>TbFeatDefine@dnd_rule_content_luban_template.xlsx</x:v>
       </x:c>
-      <x:c r="F15" s="1" t="str">
+      <x:c r="F15" s="5" t="str">
         <x:v>feat_id</x:v>
       </x:c>
-      <x:c r="G15" s="1" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H15" s="1" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="I15" s="1" t="str">
+      <x:c r="G15" s="5" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H15" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I15" s="5" t="str">
         <x:v>专长定义表</x:v>
       </x:c>
-      <x:c r="J15" s="1"/>
-      <x:c r="K15" s="1"/>
+      <x:c r="J15" s="5"/>
+      <x:c r="K15" s="5"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="1"/>
-      <x:c r="B16" s="1" t="str">
+      <x:c r="A16" s="5"/>
+      <x:c r="B16" s="5" t="str">
         <x:v>dnd.TbSpellDefine</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="str">
+      <x:c r="C16" s="5" t="str">
         <x:v>SpellDefine</x:v>
       </x:c>
-      <x:c r="D16" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="str">
+      <x:c r="D16" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" s="5" t="str">
         <x:v>TbSpellDefine@dnd_rule_content_luban_template.xlsx</x:v>
       </x:c>
-      <x:c r="F16" s="1" t="str">
+      <x:c r="F16" s="5" t="str">
         <x:v>spell_id</x:v>
       </x:c>
-      <x:c r="G16" s="1" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H16" s="1" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="I16" s="1" t="str">
+      <x:c r="G16" s="5" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H16" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I16" s="5" t="str">
         <x:v>法术定义表</x:v>
       </x:c>
-      <x:c r="J16" s="1"/>
-      <x:c r="K16" s="1"/>
-    </x:row>
-    <x:row r="17" ht="28.5">
-      <x:c r="A17" s="1"/>
-      <x:c r="B17" s="1" t="str">
+      <x:c r="J16" s="5"/>
+      <x:c r="K16" s="5"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="5"/>
+      <x:c r="B17" s="5" t="str">
         <x:v>dnd.TbClassSpellList</x:v>
       </x:c>
-      <x:c r="C17" s="1" t="str">
+      <x:c r="C17" s="5" t="str">
         <x:v>ClassSpellList</x:v>
       </x:c>
-      <x:c r="D17" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="str">
+      <x:c r="D17" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E17" s="5" t="str">
         <x:v>TbClassSpellList@dnd_rule_content_luban_template.xlsx</x:v>
       </x:c>
-      <x:c r="F17" s="1"/>
-      <x:c r="G17" s="1" t="str">
+      <x:c r="F17" s="5"/>
+      <x:c r="G17" s="5" t="str">
         <x:v>list</x:v>
       </x:c>
-      <x:c r="H17" s="1" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="I17" s="1" t="str">
+      <x:c r="H17" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I17" s="5" t="str">
         <x:v>职业法术列表关系表。业务层按 class_id + spell_id 查询。</x:v>
       </x:c>
-      <x:c r="J17" s="1"/>
-      <x:c r="K17" s="1"/>
-    </x:row>
-    <x:row r="18" ht="28.5">
-      <x:c r="A18" s="1"/>
-      <x:c r="B18" s="1" t="str">
+      <x:c r="J17" s="5"/>
+      <x:c r="K17" s="5"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="5"/>
+      <x:c r="B18" s="5" t="str">
         <x:v>dnd.TbEnumList</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="str">
+      <x:c r="C18" s="5" t="str">
         <x:v>EnumList</x:v>
       </x:c>
-      <x:c r="D18" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="str">
+      <x:c r="D18" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E18" s="5" t="str">
         <x:v>TbEnumList@dnd_rule_content_luban_template.xlsx</x:v>
       </x:c>
-      <x:c r="F18" s="1"/>
-      <x:c r="G18" s="1" t="str">
+      <x:c r="F18" s="5"/>
+      <x:c r="G18" s="5" t="str">
         <x:v>list</x:v>
       </x:c>
-      <x:c r="H18" s="1" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="I18" s="1" t="str">
+      <x:c r="H18" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I18" s="5" t="str">
         <x:v>外部枚举/字典值表。业务层按 enum_type + value 查询。</x:v>
       </x:c>
-      <x:c r="J18" s="1"/>
-      <x:c r="K18" s="1"/>
+      <x:c r="J18" s="5"/>
+      <x:c r="K18" s="5"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19"/>
-      <x:c r="B19" t="str">
+      <x:c r="A19" s="5"/>
+      <x:c r="B19" s="5" t="str">
+        <x:v>dnd.TbAlignment</x:v>
+      </x:c>
+      <x:c r="C19" s="5" t="str">
+        <x:v>Alignment</x:v>
+      </x:c>
+      <x:c r="D19" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E19" s="5" t="str">
+        <x:v>TbAlignment@dnd_rule_content_luban_template.xlsx</x:v>
+      </x:c>
+      <x:c r="F19" s="5" t="str">
+        <x:v>alignment_id</x:v>
+      </x:c>
+      <x:c r="G19" s="5" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H19" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I19" s="5" t="str">
+        <x:v>阵营定义表</x:v>
+      </x:c>
+      <x:c r="J19" s="5"/>
+      <x:c r="K19" s="5"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="5"/>
+      <x:c r="B20" s="5" t="str">
+        <x:v>dnd.TbSkillDefine</x:v>
+      </x:c>
+      <x:c r="C20" s="5" t="str">
+        <x:v>SkillDefine</x:v>
+      </x:c>
+      <x:c r="D20" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E20" s="5" t="str">
+        <x:v>TbSkillDefine@dnd_rule_content_luban_template.xlsx</x:v>
+      </x:c>
+      <x:c r="F20" s="5" t="str">
+        <x:v>skill_id</x:v>
+      </x:c>
+      <x:c r="G20" s="5" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H20" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I20" s="5" t="str">
+        <x:v>技能定义表。用于技能熟练选择等配置。</x:v>
+      </x:c>
+      <x:c r="J20" s="5"/>
+      <x:c r="K20" s="5"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="5"/>
+      <x:c r="B21" s="5" t="str">
         <x:v>dnd.TbSubclassLevelProgression</x:v>
       </x:c>
-      <x:c r="C19" t="str">
+      <x:c r="C21" s="5" t="str">
         <x:v>SubclassLevelProgression</x:v>
       </x:c>
-      <x:c r="D19" s="5" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E19" t="str">
+      <x:c r="D21" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21" s="5" t="str">
         <x:v>TbSubclassLevelProgression@dnd_rule_content_luban_template.xlsx</x:v>
       </x:c>
-      <x:c r="F19"/>
-      <x:c r="G19" t="str">
+      <x:c r="F21" s="5"/>
+      <x:c r="G21" s="5" t="str">
         <x:v>list</x:v>
       </x:c>
-      <x:c r="H19" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="I19" t="str">
+      <x:c r="H21" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I21" s="5" t="str">
         <x:v>子职业按主职业等级成长表。</x:v>
       </x:c>
-      <x:c r="J19"/>
-      <x:c r="K19"/>
+      <x:c r="J21" s="5"/>
+      <x:c r="K21" s="5"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="5"/>
+      <x:c r="B22" s="5" t="str">
+        <x:v>dnd.TbDndItemDefine</x:v>
+      </x:c>
+      <x:c r="C22" s="5" t="str">
+        <x:v>DndItemDefine</x:v>
+      </x:c>
+      <x:c r="D22" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" s="5" t="str">
+        <x:v>TbDndItemDefine@dnd_rule_content_luban_template.xlsx</x:v>
+      </x:c>
+      <x:c r="F22" s="5" t="str">
+        <x:v>item_id</x:v>
+      </x:c>
+      <x:c r="G22" s="5" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H22" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I22" s="5" t="str">
+        <x:v>DnD 物品定义表。</x:v>
+      </x:c>
+      <x:c r="J22" s="5"/>
+      <x:c r="K22" s="5"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="5"/>
+      <x:c r="B23" s="5" t="str">
+        <x:v>dnd.TbDndToolDefine</x:v>
+      </x:c>
+      <x:c r="C23" s="5" t="str">
+        <x:v>DndToolDefine</x:v>
+      </x:c>
+      <x:c r="D23" s="10" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E23" s="5" t="str">
+        <x:v>TbDndToolDefine@dnd_rule_content_luban_template.xlsx</x:v>
+      </x:c>
+      <x:c r="F23" s="5" t="str">
+        <x:v>tool_id</x:v>
+      </x:c>
+      <x:c r="G23" s="5" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H23" s="5" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I23" s="5" t="str">
+        <x:v>DnD 工具定义表</x:v>
+      </x:c>
+      <x:c r="J23" s="5"/>
+      <x:c r="K23" s="5"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24"/>
+      <x:c r="B24" t="str">
+        <x:v>dnd.TbDndLanguageDefine</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>DndLanguageDefine</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>TbDndLanguageDefine@dnd_rule_content_luban_template.xlsx</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>language_id</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I24" t="str">
+        <x:v>DnD 语言定义表</x:v>
+      </x:c>
+      <x:c r="J24"/>
+      <x:c r="K24"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R30f70c69fc5c4c7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3c43c37a1e9e45b2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -957,6 +957,35 @@
       <x:c r="J24"/>
       <x:c r="K24"/>
     </x:row>
+    <x:row r="25">
+      <x:c r="A25"/>
+      <x:c r="B25" t="str">
+        <x:v>dnd.TbTextLocalize</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>TextLocalize</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>TbTextLocalize@dnd_rule_content_luban_template.xlsx</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>text_key</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>DnD text localization table</x:v>
+      </x:c>
+      <x:c r="J25"/>
+      <x:c r="K25"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
